--- a/public/downloads/templates/negative-keyword-master-list-template.xlsx
+++ b/public/downloads/templates/negative-keyword-master-list-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="How to use" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Negative Keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Negative Keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -490,6 +490,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -525,8 +526,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Project Amazon PH Academy — Download Center</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1023,5 +1039,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>